--- a/sales_analysis_report.xlsx
+++ b/sales_analysis_report.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>727851.12</v>
+        <v>694638.8300000001</v>
       </c>
     </row>
     <row r="3">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3693</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="4">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1091.231064467766</v>
+        <v>1043.001246246246</v>
       </c>
     </row>
   </sheetData>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>166126.57</v>
+        <v>166679.76</v>
       </c>
       <c r="C2" t="n">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="3">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>176352.72</v>
+        <v>171992.53</v>
       </c>
       <c r="C3" t="n">
-        <v>901</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>191089.05</v>
+        <v>180964.33</v>
       </c>
       <c r="C4" t="n">
-        <v>998</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>194282.78</v>
+        <v>175002.21</v>
       </c>
       <c r="C5" t="n">
-        <v>917</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -597,11 +597,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>123932.06</v>
+        <v>107541.34</v>
       </c>
     </row>
     <row r="3">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113973.23</v>
+        <v>103896.39</v>
       </c>
     </row>
     <row r="4">
@@ -621,27 +621,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108973.15</v>
+        <v>101721.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>104794.89</v>
+        <v>100035.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Desk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95306.72</v>
+        <v>95507.02</v>
       </c>
     </row>
   </sheetData>
@@ -673,11 +673,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88066.07000000001</v>
+        <v>1418.52</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>92805</v>
+        <v>91137.62</v>
       </c>
     </row>
     <row r="4">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95306.72</v>
+        <v>93380.63</v>
       </c>
     </row>
   </sheetData>
@@ -729,21 +729,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>298599.43</v>
+        <v>263779.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>249091.24</v>
+        <v>238745.62</v>
       </c>
     </row>
     <row r="4">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180160.45</v>
+        <v>192113.39</v>
       </c>
     </row>
   </sheetData>
@@ -785,21 +785,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Debit Card</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>155511.12</v>
+        <v>173131.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Debit Card</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>151822.53</v>
+        <v>150108.09</v>
       </c>
     </row>
     <row r="4">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150025.92</v>
+        <v>139033.43</v>
       </c>
     </row>
     <row r="5">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143380.67</v>
+        <v>129380.75</v>
       </c>
     </row>
     <row r="6">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127110.88</v>
+        <v>102985</v>
       </c>
     </row>
   </sheetData>

--- a/sales_analysis_report.xlsx
+++ b/sales_analysis_report.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>694638.8300000001</v>
+        <v>727851.12</v>
       </c>
     </row>
     <row r="3">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3658</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="4">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1043.001246246246</v>
+        <v>1091.231064467766</v>
       </c>
     </row>
   </sheetData>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>166679.76</v>
+        <v>166126.57</v>
       </c>
       <c r="C2" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="3">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171992.53</v>
+        <v>176352.72</v>
       </c>
       <c r="C3" t="n">
-        <v>889</v>
+        <v>901</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180964.33</v>
+        <v>191089.05</v>
       </c>
       <c r="C4" t="n">
-        <v>968</v>
+        <v>998</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>175002.21</v>
+        <v>194282.78</v>
       </c>
       <c r="C5" t="n">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -597,11 +597,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107541.34</v>
+        <v>123932.06</v>
       </c>
     </row>
     <row r="3">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103896.39</v>
+        <v>113973.23</v>
       </c>
     </row>
     <row r="4">
@@ -621,27 +621,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101721.83</v>
+        <v>108973.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100035.48</v>
+        <v>104794.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95507.02</v>
+        <v>95306.72</v>
       </c>
     </row>
   </sheetData>
@@ -673,11 +673,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Desk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1418.52</v>
+        <v>88066.07000000001</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91137.62</v>
+        <v>92805</v>
       </c>
     </row>
     <row r="4">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93380.63</v>
+        <v>95306.72</v>
       </c>
     </row>
   </sheetData>
@@ -729,21 +729,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263779.82</v>
+        <v>298599.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>238745.62</v>
+        <v>249091.24</v>
       </c>
     </row>
     <row r="4">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>192113.39</v>
+        <v>180160.45</v>
       </c>
     </row>
   </sheetData>
@@ -785,21 +785,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Debit Card</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173131.56</v>
+        <v>155511.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Debit Card</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150108.09</v>
+        <v>151822.53</v>
       </c>
     </row>
     <row r="4">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139033.43</v>
+        <v>150025.92</v>
       </c>
     </row>
     <row r="5">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>129380.75</v>
+        <v>143380.67</v>
       </c>
     </row>
     <row r="6">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102985</v>
+        <v>127110.88</v>
       </c>
     </row>
   </sheetData>

--- a/sales_analysis_report.xlsx
+++ b/sales_analysis_report.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>694638.8300000001</v>
+        <v>785153.6000000001</v>
       </c>
     </row>
     <row r="3">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3658</v>
+        <v>3706</v>
       </c>
     </row>
     <row r="4">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1043.001246246246</v>
+        <v>1177.141829085457</v>
       </c>
     </row>
   </sheetData>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>166679.76</v>
+        <v>189495.83</v>
       </c>
       <c r="C2" t="n">
-        <v>879</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171992.53</v>
+        <v>190046.88</v>
       </c>
       <c r="C3" t="n">
-        <v>889</v>
+        <v>929</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>180964.33</v>
+        <v>222955.66</v>
       </c>
       <c r="C4" t="n">
-        <v>968</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>175002.21</v>
+        <v>182655.23</v>
       </c>
       <c r="C5" t="n">
-        <v>922</v>
+        <v>862</v>
       </c>
     </row>
   </sheetData>
@@ -597,51 +597,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107541.34</v>
+        <v>137523.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103896.39</v>
+        <v>124028.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Desk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101721.83</v>
+        <v>111776.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100035.48</v>
+        <v>107715.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95507.02</v>
+        <v>107105.92</v>
       </c>
     </row>
   </sheetData>
@@ -673,11 +673,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1418.52</v>
+        <v>97754.29000000001</v>
       </c>
     </row>
     <row r="3">
@@ -687,17 +687,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91137.62</v>
+        <v>99250.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93380.63</v>
+        <v>107105.92</v>
       </c>
     </row>
   </sheetData>
@@ -729,21 +729,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263779.82</v>
+        <v>319319.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>238745.62</v>
+        <v>281547.58</v>
       </c>
     </row>
     <row r="4">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>192113.39</v>
+        <v>184286.55</v>
       </c>
     </row>
   </sheetData>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173131.56</v>
+        <v>173767.15</v>
       </c>
     </row>
     <row r="3">
@@ -799,37 +799,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150108.09</v>
+        <v>168537.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Gift Card</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139033.43</v>
+        <v>152288.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>129380.75</v>
+        <v>146722.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gift Card</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102985</v>
+        <v>143837.81</v>
       </c>
     </row>
   </sheetData>

--- a/sales_analysis_report.xlsx
+++ b/sales_analysis_report.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>785153.6000000001</v>
+        <v>727851.12</v>
       </c>
     </row>
     <row r="3">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3706</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1177.141829085457</v>
+        <v>1091.231064467766</v>
       </c>
     </row>
   </sheetData>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>189495.83</v>
+        <v>166126.57</v>
       </c>
       <c r="C2" t="n">
-        <v>874</v>
+        <v>877</v>
       </c>
     </row>
     <row r="3">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>190046.88</v>
+        <v>176352.72</v>
       </c>
       <c r="C3" t="n">
-        <v>929</v>
+        <v>901</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>222955.66</v>
+        <v>191089.05</v>
       </c>
       <c r="C4" t="n">
-        <v>1041</v>
+        <v>998</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>182655.23</v>
+        <v>194282.78</v>
       </c>
       <c r="C5" t="n">
-        <v>862</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -597,51 +597,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>137523.86</v>
+        <v>123932.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>124028.1</v>
+        <v>113973.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Desk</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>111776.05</v>
+        <v>108973.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>107715.33</v>
+        <v>104794.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>107105.92</v>
+        <v>95306.72</v>
       </c>
     </row>
   </sheetData>
@@ -673,11 +673,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Desk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97754.29000000001</v>
+        <v>88066.07000000001</v>
       </c>
     </row>
     <row r="3">
@@ -687,17 +687,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99250.05</v>
+        <v>92805</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107105.92</v>
+        <v>95306.72</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>319319.47</v>
+        <v>298599.43</v>
       </c>
     </row>
     <row r="3">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>281547.58</v>
+        <v>249091.24</v>
       </c>
     </row>
     <row r="4">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>184286.55</v>
+        <v>180160.45</v>
       </c>
     </row>
   </sheetData>
@@ -785,51 +785,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Debit Card</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>173767.15</v>
+        <v>155511.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Debit Card</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>168537.45</v>
+        <v>151822.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gift Card</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>152288.46</v>
+        <v>150025.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>146722.73</v>
+        <v>143380.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Gift Card</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>143837.81</v>
+        <v>127110.88</v>
       </c>
     </row>
   </sheetData>
